--- a/logs/Consolidado_27_04_2026.xlsx
+++ b/logs/Consolidado_27_04_2026.xlsx
@@ -638,10 +638,10 @@
         <v>152</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -657,10 +657,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -676,10 +676,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -695,10 +695,10 @@
         <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -714,10 +714,10 @@
         <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -733,10 +733,10 @@
         <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -752,10 +752,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1227,40 +1227,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Body Moisturizing Melt-In Balm
 Bálsamo Hidratante Pele Desidratada
 250 ml</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/body-moisturizing-melt-in-balm-6403032.html</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>6403032</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2284,39 +2284,39 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Coffret Natal Men Duo Espuma Barbear
 2 x 200 ml</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/coffret-natal-men-duo-espuma-barbear-7648277.html</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>7648277</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -2562,40 +2562,40 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Couvrance Eyebrow and Eye Pencil Blond
 Lápis para Sobrancelhas e Olhos
 1,45 ml</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/couvrance-eyebrow-and-eye-pencil-blond-4166734.html</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>4166734</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -2882,40 +2882,40 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Couvrance Illuminating Mosaic Powder
 Pó Compacto Matificante e Fixador
 9 gr</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/couvrance-illuminating-mosaic-powder-5662112.html</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>5662112</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -3522,40 +3522,40 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Hyaluron Activ B3 Refill Cell Renewal Cream
 Recarga Creme Dia Rugas AH Niacinamida
 50 ml</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/hyaluron-activ-b3-refill-cell-renewal-cream-7654172.html</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr"/>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>7654172</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -4365,43 +4365,43 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>Micelar Water Make-Up Removing
 Água Micelar Desmaquilhante Pele Sensível</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/micelar-water-make-up-removing-443917.html</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>8690955</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5293,40 +5293,40 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>Sun Care Oil Sensitive Skin SPF30
 Protetor Solar Óleo Não Pegajoso Corpo
 200 ml</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sun-care-oil-sensitive-skin-spf30-5272722.html</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr"/>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr"/>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
         <is>
           <t>5272722</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -5373,40 +5373,40 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>Sun Care Silky Mist Sensitive Skin SPF30
 Protetor Solar Bruma Acetinada Rosto e Corpo
 150 ml</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sun-care-silky-mist-sensitive-skin-spf30-6511556.html</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>6511556</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5493,40 +5493,40 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>Sun Care Spray Sensitive Skin SPF20
 Protetor Solar Spray Corpo Pele Sensível
 200 ml</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sun-care-spray-sensitive-skin-spf20-3065957.html</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr"/>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
         <is>
           <t>3065957</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5772,40 +5772,40 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>Sun Care Tinted Compact Beige SPF50+
 Protetor Solar de Rosto Compacto
 10gr</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sun-care-tinted-compact-beige-spf50-3065906.html</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr"/>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr"/>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
         <is>
           <t>3065906</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7070,83 +7070,83 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C157" s="5" t="inlineStr">
+      <c r="C157" s="7" t="inlineStr">
         <is>
           <t>Xeracalm AD Lipid-Replenishing Cleansing Oil
 Óleo de Limpeza Pele Seca Atópica Comichão</t>
         </is>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D157" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/xeracalm-ad-lipid-replenishing-cleansing-oil-457216.html</t>
         </is>
       </c>
-      <c r="E157" s="5" t="inlineStr">
+      <c r="E157" s="7" t="inlineStr">
         <is>
           <t>1000 ml</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="inlineStr">
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
         <is>
           <t>8804160</t>
         </is>
       </c>
-      <c r="H157" s="5" t="inlineStr">
+      <c r="H157" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C158" s="7" t="inlineStr">
         <is>
           <t>Xeracalm AD Replenshing Milky Gel
 Gel Lácteo Acalma Comichão Pele Seca Atópica
 200 ml</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D158" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/xeracalm-ad-replenshing-milky-gel-8726971.html</t>
         </is>
       </c>
-      <c r="E158" s="3" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="E158" s="7" t="inlineStr"/>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
         <is>
           <t>8726971</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7708,40 +7708,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Bálsamo Emoliente Antiprurido Dexyane
 Bálsamo Antiprurido Pele Seca e Eczema Atópico
 400 ml</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/balsamo-emoliente-antiprurido-dexyane-5976214.html</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>5976214</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7828,40 +7828,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Creme Emoliente Antiprurido Dexyane
 Creme Antiprurido Pele Seca e Eczema Atópico
 400 ml</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-emoliente-antiprurido-dexyane-5976217.html</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>5976217</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -8108,40 +8108,40 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Dexyane Anti-Scratching Emollient Cream
 Creme Rosto Corpo Pele Seca Eczema e Atópica
 200 ml</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dexyane-anti-scratching-emollient-cream-5976215.html</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>5976215</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -8354,40 +8354,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Extra Doux Shampooing Dermo-Protecteur
 Champô Ultra Suave para Uso Familiar
 100 ml</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/extra-doux-shampooing-dermo-protecteur-5797814.html</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>5797814</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -8480,40 +8480,40 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Gel de Limpeza Pele Seca e Atópica Dexyane
 Gel de Limpeza Calmante Pele Seca e Atópica
 400 ml</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-de-limpeza-pele-seca-e-atopica-dexyane-5976219.html</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>5976219</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -8720,120 +8720,120 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Kelual Squanorm Anti-Dandruff Refresh Lotion
 Loção Leave-in Refrescante Cabelo com Caspa
 190 ml</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-anti-dandruff-refresh-lotion-8660190.html</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>8660190</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Kelual Squanorm Anti-Dandruff Refreshing
 Champô Resfrescante Cabelo com Caspa
 400 ml</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-anti-dandruff-refreshing-8660180.html</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>8660180</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Kelual Squanorm Anti-Dandruff Refreshing
 Champô Resfrescante Cabelo com Caspa
 200 ml</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-anti-dandruff-refreshing-8710845.html</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>8710845</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -9174,80 +9174,80 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Lotion Purifiante
 Loção Purificante Acne Matifica e Fecha Poros
 200 ml</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-lotion-purifiante-3891879.html</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>3891879</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Mat 12H Oily Skin
 Gel Matificante Pele Oleosa Ação Anti-brilho
 30 ml</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-mat-12h-oily-skin-6037944.html</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>6037944</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9294,40 +9294,40 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Repair Baume Lèvres
 Bálsamo Lábios Gretados e Danificados Acne
 15 ml</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-repair-baume-levres-5410512.html</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>5410512</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9374,160 +9374,160 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Stop Care Drying Gel
 Gel SOS Localizado Stop Acne e Borbulhas
 10 ml</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-stop-care-drying-gel-3601988.html</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>3601988</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Kertyol PSO Cleansing Gel
 Gel de Limpeza Rosto Ultra Rico Pele Psoríase
 400 ml</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-cleansing-gel-8487441.html</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>8487441</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Kertyol PSO Daily Balm
 Bálsamo Corpo Hidratante Pele com Psoríase
 200 ml</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-daily-balm-8487355.html</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>8487355</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Kertyol PSO Daily Balm
 Bálsamo Corpo Hidratante Pele com Psoríase
 400 ml</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-daily-balm-8487356.html</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>8487356</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -9614,120 +9614,120 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Melascreen Concentré Antitaches Brunes
 Creme Rosto Concentrado Antimanchas
 30 ml</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/melascreen-concentre-antitaches-brunes-7850405.html</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>7850405</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Melascreen Contour des Yeux Antitaches
 Creme de Olhos Iluminador Antimanchas
 15 ml</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/melascreen-contour-des-yeux-antitaches-7850428.html</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>7850428</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Melascreen Crème Antitaches Brunes
 Creme de Rosto Antimanchas Pele Seca SPF50+
 50 ml</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/melascreen-creme-antitaches-brunes-7850426.html</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>7850426</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9934,40 +9934,40 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Sabal Argeal Shampooing Quotidien Sébo-Absorbant
 Champô Sebo-absorvente Cabeelo Oleoso
 200 ml</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sabal-argeal-shampooing-quotidien-sebo-absorbant-8471871.html</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>8471871</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -10014,40 +10014,40 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Sensinol Physio-Protective Soothing Body
 Leite Corpo Calmante Fisioprotetor Pele Seca
 400 ml</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sensinol-physio-protective-soothing-body-6606368.html</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>6606368</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10134,126 +10134,126 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>Sensinol Soothing Cleansing Oil
 Óleo Lavante Calmante Pele Seca Comichão</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sensinol-soothing-cleansing-oil-415426.html</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>6037950</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Sensinol Soothing Cleansing Oil
 Óleo Lavante Calmante Pele Seca Comichão</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sensinol-soothing-cleansing-oil-415426.html</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>6606367</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Solução Aquosa Diaseptyl
 Solução Antissética com Clorexidina 0,2%
 125 ml</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/solucao-aquosa-diaseptyl-6869813.html</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>6869813</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10529,40 +10529,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Bebé Multi-Purpose Oil BIO
 Óleo Multiusos BIO Limpa Nutre desde 0 meses
 200 ml</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-multi-purpose-oil-bio-7831747.html</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>7831747</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10609,40 +10609,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Bebé Nourishing Cream With Cold Cream
 Creme Nutritivo Pele Seca 0 meses
 125 ml</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-nourishing-cream-with-cold-cream-6661554.html</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>6661554</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
@@ -10769,40 +10769,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Centaury Anti-Yellowing Neutral Conditioner
 Condicionador CentáureaBIO Neutraliza Amarelo
 200 ml</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/centaury-anti-yellowing-neutral-conditioner-7447294.html</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>7447294</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -11055,80 +11055,80 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Crème Solaire Sublime SPF 30
 Protetor Solar de Rosto Antienvelhecimento
 50 ml</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-solaire-sublime-spf-30-7129218.html</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>7129218</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Crème Solaire Sublime SPF 50+
 Protetor Solar de Rosto Antienvelhecimento
 50 ml</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-solaire-sublime-spf-50-7129219.html</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>7129219</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -11175,40 +11175,40 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Creme Duche Nutritivo
 Creme Duche Hidratante e Nutritivo Cupuaçu
 200 ml</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-creme-duche-nutritivo-6515197.html</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>6515197</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -11335,40 +11335,40 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Gel Duche Nutritivo Figuier
 Gel Duche Hidratante e Nutritivo Figueira
 200 ml</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-gel-duche-nutritivo-figuier-7724345.html</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>7724345</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -11495,40 +11495,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Cupuaçu Reparing Very Dry Hair Shampoo
 Champô Cupuaçu BIO Repara Cabelo Muito Seco
 400 ml</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-reparing-very-dry-hair-shampoo-343983.html</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>7104602</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -11614,43 +11614,43 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Flax Volume Fine Hair Shampoo
 Champô Fibras de Linho BIO Volume Cabelo Fino</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>5221797</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -11826,40 +11826,40 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Gel-Crème Solaire Sublime SPF 30
 Protetor Solar de Corpo Nutritivo
 200 ml</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-creme-solaire-sublime-spf-30-7129220.html</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>7129220</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -11905,39 +11905,39 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Grenade Éclat Couleur Shampooing
 Champô Iluminador e Potenciador de Cor</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/grenade-eclat-couleur-shampooing-3688252.html</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>3688252</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -12110,120 +12110,120 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Hair Removal Cream Sweet Almond
 Creme Depilatório pele Sensível Amêndoas Doce
 150 ml</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/hair-removal-cream-sweet-almond-7724355.html</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>7724355</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Huile Réparatrice Après-Soleil
 Óleo Protetor de Cabelo Nutritivo
 150 ml</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/huile-reparatrice-apres-soleil-7546027.html</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>7546027</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Huile Sèche Solaire SPF 30
 Protetor Solar de Corpo e Cabelo
 200 ml</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/huile-seche-solaire-spf-30-7129222.html</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>7129222</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -12389,80 +12389,80 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Manga Nourishing Conditioner
 Condicionador Manga Nutritivo Cabelo Seco
 50 ml</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-conditioner-343975.html</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>6128332</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Leave-In Cream
 Creme Dia Manga Nutritivo SOS Cabelo Seco
 125ml</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-leave-in-cream-5072223.html</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>5072223</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -12509,43 +12509,43 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Shampoo
 Champô Manga Nutritivo para Cabelo Seco</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>3018059</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -12678,83 +12678,83 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Nettle &amp; Clay 2-in-1 Mask Shampoo
 Máscara Champô Pó Ortiga BIO Cabelo Oleoso
 150 ml</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-clay-2-in-1-mask-shampoo-7339155.html</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>7339155</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
 Champô Seco Ortiga BIO Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>8123735</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -12930,43 +12930,43 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
 Champô Seco Aveia Spray Suave Cabelo Normal</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>7831152</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -13723,40 +13723,40 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Protective Powder Bio
 Pó Talco Protetor para Bebé
 75 gr</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/protective-powder-bio-8486142.html</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>8486142</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
@@ -14052,40 +14052,40 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>Tamanu &amp; Monoi Nutri-Repair Sun Shampoo
 Champô Protetor Solar Cabelo Exposto ao Sol
 200 ml</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/tamanu-and-monoi-nutri-repair-sun-shampoo-7396246.html</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
         <is>
           <t>7396246</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -14132,40 +14132,40 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Tamanu BIO e Monoi Spray Solar Sublime SPF30
 Protetor Solar Spray Corpo Sublimador
 200 ml</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/tamanu-bio-e-monoi-spray-solar-sublime-spf30-7129223.html</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>7129223</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14241,160 +14241,160 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>5 Sens Enhancing Detangling Conditioner
 Bálsamo Cabelo Sublimador Desembaraçador
 200 ml</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/5-sens-enhancing-detangling-conditioner-6218355.html</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>6218355</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>5 Sens Enhancing Dry Oil Hair &amp; Body
 Óleo Seco Sublimador para Cabelo e Corpo
 100 ml</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/5-sens-enhancing-dry-oil-hair-and-body-5558999.html</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>5558999</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>5 Sens Enhancing Shampoo Frequent Use
 Champô Sublimador Realça o Brilho
 250 ml</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/5-sens-enhancing-shampoo-frequent-use-6218353.html</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>6218353</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>5 Sens Enhancing Shower Oil
 Óleo de Duche Sublimador 5 Sens
 200 ml</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/5-sens-enhancing-shower-oil-7294935.html</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>7294935</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -14441,80 +14441,80 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Absolue Kératine Repairing Beauty Cream
 Creme Leave-In Reparador Cabelo Danificado
 100 ml</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/absolue-keratine-repairing-beauty-cream-6997974.html</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>6997974</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Absolue Kératine Repairing Mask
 Máscara Reparadora Cabelo Grosso Danificado
 200ml</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/absolue-keratine-repairing-mask-6997986.html</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>6997986</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14561,40 +14561,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Absolue Kératine Repairing Shampoo
 Champô Reparador Cabelo Danificado Frágil
 200 ml</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/absolue-keratine-repairing-shampoo-6997972.html</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>6997972</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -14641,40 +14641,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Astera Fresh Soothing Freshness Shampoo
 Champô Calmante Couro Cabeludo Irritado
 200 ml</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/astera-fresh-soothing-freshness-shampoo-5520033.html</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>5520033</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -14721,80 +14721,80 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Color Glow Protecting Color Shampoo
 Champô Protetor Cor Cabelo Pintado e Madeixas
 200 ml</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/color-glow-protecting-color-shampoo-7924431.html</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>7924431</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Color Glow Repairing Glow Conditioner
 Máscara Reparadora Cabelo Pintado e Madeixas
 200 ml</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/color-glow-repairing-glow-conditioner-7924433.html</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>7924433</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14841,80 +14841,80 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Curbicia Scalp Prone to Oiliness Shampoo
 Champô Equilibrante Couro Cabeludo Oleoso
 150 ml</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/curbicia-scalp-prone-to-oiliness-shampoo-5520011.html</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>5520011</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Forticea Energizing Lotion
 Loção Leave-In Fortificante Todos Tipo Cabelo
 100 ml</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/forticea-energizing-lotion-6490926.html</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>6490926</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -14964,43 +14964,43 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Forticea Strengthening Revitalizing Shampoo
 Champô Fortificante Todos Tipos de Cabelo</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>7630905</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -15047,40 +15047,40 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Head Spa Astera Soothing Freshness &amp; Purity
 Pré-Champô Couro Cabeludo Irritado
 50 ml</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/head-spa-astera-soothing-freshness-and-purity-5520225.html</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>5520225</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -15127,119 +15127,119 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Head Spa Purifying Scrub Detox
 Esfoliante Pré-Champô Couro Cabeludo Oleoso
 150 ml</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/head-spa-purifying-scrub-detox-7824621.html</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>7824621</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Laca Sytle
 100 ml</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/laca-sytle-7447298.html</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>7447298</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Naturia Detangling Milky Conditioner
 Condicionador Suave Uso Frequente e Familiar
 150 ml</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-detangling-milky-conditioner-7649340.html</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>7649340</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -15286,129 +15286,129 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>5522799</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>6633968</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>7610972</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -15495,280 +15495,280 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Naturia Invisible Dry Shampoo
 Champô Seco Invisível Lavanda Orgânica
 75 ml</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-invisible-dry-shampoo-7716350.html</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>7716350</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Okara Blond Brightening Conditioner Blond Hair
 Condicionador Brilho Louro Natural ou Pintado
 150 ml</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/okara-blond-brightening-conditioner-blond-hair-6760082.html</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>6760082</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Okara Blond Brightening Shampoo Blond Hair
 Champô Iluminador Louro Natural ou Pintado
 200 ml</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/okara-blond-brightening-shampoo-blond-hair-6760061.html</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>6760061</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Okara Blond Brightening Spray Blond Hair
 Spray Cabelo Iluminador Louro Natural ou Pintado
 150 ml</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/okara-blond-brightening-spray-blond-hair-6761000.html</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>6761000</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Okara Silver Toning Shampoo
 Champô Violeta Cabelo Branco Grisalho ou Louro
 200 ml</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/okara-silver-toning-shampoo-6759950.html</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>6759950</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Solaire Nourishing Repair Shampoo
 Champô Reparação Nutritiva Pós-Sol e Cloro
 200 ml</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/solaire-nourishing-repair-shampoo-5520120.html</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>5520120</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Solaire Sun Repair Ritual Nourishing Shower Gel
 Gel Banho Cabelo e Corpo Pós-Sol Cloro
 200 ml</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/solaire-sun-repair-ritual-nourishing-shower-gel-5520162.html</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>5520162</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -15815,280 +15815,280 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Solaire Sun Ritual Protective Oil KPF50+
 Protetor Solar Óleo para o Cabelo
 100 ml</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/solaire-sun-ritual-protective-oil-kpf50-5520294.html</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>5520294</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Style Finishing Spray Hold &amp; Shine
 Laca Fixação Forte Efeito Anti-humidade
 300 ml</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/style-finishing-spray-hold-and-shine-7447297.html</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>7447297</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Style Holding Gel Sculpt &amp; Hold
 Gel Cabelo Fixação Sem Resíduos Efeito Wet Look
 150 ml</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/style-holding-gel-sculpt-and-hold-7447300.html</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>7447300</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Style Holding Spray Precise &amp; Strong
 Spray Cabelo Fixação Ultra-Forte Longa Duração
 150 ml</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/style-holding-spray-precise-and-strong-7447299.html</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>7447299</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Style Modeling Paste
 Pasta para Cabelo Modeladora Fixação Natural
 75 ml</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/style-modeling-paste-7447301.html</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>7447301</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Style Sculpting Mousse Volume &amp; Sculpt
 Espuma Cabelo Modeladora Volumizadora da Raiz
 200 ml</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/style-sculpting-mousse-volume-and-sculpt-7447302.html</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>7447302</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Style Texture Spray Volume &amp; Hold
 Spray Cabelo Texturizante Volumizador da Raiz
 200 ml</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/style-texture-spray-volume-and-hold-7447303.html</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>7447303</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16135,80 +16135,80 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Sublime Curl Activating Detangling Conditioner
 Condicionador Suave e Redefinidor de Caracóis
 150 ml</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-curl-activating-detangling-conditioner-5972162.html</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>5972162</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Sublime Curl Activating Spray Wavy Curly Hair
 Spray Cabelo Leave-In Redefinidor de Caracóis
 150 ml</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-curl-activating-spray-wavy-curly-hair-6490914.html</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>6490914</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16255,200 +16255,200 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Sublime Karité Moisturizing Smooting Mask
 Máscara Hidratante Cabelo Desidratado
 200 ml</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-karite-moisturizing-smooting-mask-8109685.html</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>8109685</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Sublime Karité Moisturizing Smooting Shampoo
 Champô Hidratante Cabelo Seco e Muito Seco
 200 ml</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-karite-moisturizing-smooting-shampoo-8109682.html</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>8109682</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Sublime Karité Professional Smooting Milk
 Leite Capilar Hidratante Anti-frizz Disciplina
 100 ml</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-karite-professional-smooting-milk-8109683.html</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>8109683</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Sublime Karité Professional Taming Cream
 Creme Nutritivo Anti-frizz Cabelo Muito Seco
 100 ml</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-karite-professional-taming-cream-8109706.html</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>8109706</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Sublime Karité Taming Nourishing Mask
 Máscara Nutritiva Cabelo Muito Seco
 200 ml</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sublime-karite-taming-nourishing-mask-8109707.html</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>8109707</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -16495,40 +16495,40 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Tonucia Natural Filler Youth Serum
 Sérum Leave-In Densificador Cabelo Enfraquecido
 75ml</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/tonucia-natural-filler-youth-serum-7340492.html</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>7340492</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16701,40 +16701,40 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Triphasic Anti-Hair Loss Shampoo
 Champô Queda de Cabelo com Óleos Essenciais
 200 ml</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-anti-hair-loss-shampoo-6458824.html</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>6458824</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16781,40 +16781,40 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Triphasic Anti-Hair Loss Shampoo
 Champô Queda de Cabelo com Óleos Essenciais
 50 ml</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-anti-hair-loss-shampoo-7630904.html</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>7630904</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -16861,40 +16861,40 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Triphasic Caps Lunghezze
 Cápsulas Crescimento e Força do Cabelo
 90 cápsulas</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/triphasic-caps-lunghezze-8612382.html</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>8612382</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -17061,40 +17061,40 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>Volumea Volumizing Conditioner
 Bálsamo Volumizador Cabelo Fino sem Volume
 150 ml</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/volumea-volumizing-conditioner-5520279.html</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>5520279</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -17141,40 +17141,40 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>Volumea Volumizing Shampoo
 Champô Volumizador Cabelo Fino sem Volume
 200 ml</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/volumea-volumizing-shampoo-5520117.html</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>5520117</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="7" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -17530,203 +17530,203 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Cutalgan Refreshing Spray Ultra-Calming
 Spray Refrescante Ultra Calmante Pele Irritada
 100 ml</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cutalgan-refreshing-spray-ultra-calming-7106558.html</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>7106558</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Cutalgan Sting Overheating Roll-on
 Roll-on Refresca Ultra Calmante Pele Irritada
 10 ml</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cutalgan-sting-overheating-roll-on-8124492.html</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>8124492</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Cytelium Drying Lotion Soothing
 Loção Secante Suavizante Pele Irritada
 100 ml</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cytelium-drying-lotion-soothing-3691921.html</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>3691921</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Cytelium Drying Spray Soothing
 Spray Secante Suavizante Pele Irritada
 100 ml</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cytelium-drying-spray-soothing-3692048.html</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>3692048</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Dermalibour+ Barrier Irritaded Aggressed Skin
 Creme Barreira Protetor Isolante Pele Irritada</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dermalibour-barrier-irritaded-aggressed-skin-452822.html</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>6554645</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -17991,43 +17991,43 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Epitheliale Ultra Repair Cream SPF50+
 Creme Protetor Solar Reparador</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/epitheliale-ultra-repair-cream-spf50-412214.html</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>40 ml</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>8478836</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -18114,40 +18114,40 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Epitheliale Ultra Repair Serum HA+
 Sérum Rosto Multireparador Regenerador
 30 ml</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/epitheliale-ultra-repair-serum-ha-8478839.html</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>8478839</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -18790,43 +18790,43 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Exomega Control Emollient Foaming Gel
 Gel Espuma Calmante Comichão da Pele Atópica</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emollient-foaming-gel-452816.html</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>6587158</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -19328,40 +19328,40 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Primalba 2 in 1 Cleansing Gel Body and Hair
 Gel de Banho Corpo e Cabelo Recém Nascidos
 500 ml</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/primalba-2-in-1-cleansing-gel-body-and-hair-3020294.html</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>3020294</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19527,39 +19527,39 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Protect Cream SPF50+
 Protetor Solar Creme Rosto Sem Perfume</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/protect-cream-spf50-6902188.html</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>6902188</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19686,39 +19686,39 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Protect Lotion SPF50+
 Protetor Sola Leite Rosto Corpo Pele Sensível</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/protect-lotion-spf50-6902145.html</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>6902145</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -20238,40 +20238,40 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Colutório Júnior Emoji
 500 ml</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/colutorio-junior-emoji-7607830.html</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>7607830</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -20318,40 +20318,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Dentífrico Kids Timer
 50 ml</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dentifrico-kids-timer-7616572.html</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>7616572</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -20478,40 +20478,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Elgydium Fix Fixação Forte
 45 g</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/elgydium-fix-fixacao-forte-7434256.html</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>7434256</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -21119,40 +21119,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Kids Emoji
 1 un</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-kids-emoji-7607814.html</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>7607814</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -21199,17 +21199,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Medium 4 in 1
@@ -21217,23 +21217,23 @@
 1 un</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-medium-4-in-1-8437467.html</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>8437467</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -21280,40 +21280,40 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Ortodôntica 7-12 Anos
 1 un</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-ortodontica-7-12-anos-4031802.html</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>4031802</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -21360,40 +21360,40 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Pocket Suave
 1 un</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-pocket-suave-6259714.html</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>6259714</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -21440,17 +21440,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova de Dentes Soft 4 in 1
@@ -21458,23 +21458,23 @@
 1 un</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-de-dentes-soft-4-in-1-8436212.html</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>8436212</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -21601,40 +21601,40 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Eco Suave
 1 un</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-eco-suave-7434319.html</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>7434319</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -21681,40 +21681,40 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Dentes Próteses Dentárias
 1 un</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-dentes-proteses-dentarias-4907334.html</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>4907334</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -21761,40 +21761,40 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escova Style Reciclada Média
 1 un</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escova-style-reciclada-media-7697229.html</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>7697229</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -21961,40 +21961,40 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Clinic Mono Compact Verde
 4 un</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-clinic-mono-compact-verde-5815553.html</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>5815553</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -22041,17 +22041,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Interdentário Laranja
@@ -22059,40 +22059,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-interdentario-laranja-8420655.html</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>8420655</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Recarga ISO1
@@ -22100,40 +22100,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-recarga-iso1-8478522.html</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>8478522</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Escovilhão Recarga ISO4
@@ -22141,23 +22141,23 @@
 1 un</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/escovilhao-recarga-iso4-8478523.html</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>8478523</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -22285,40 +22285,40 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Fio Dentário Black
 1 un</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/fio-dentario-black-5786948.html</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>5786948</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -23008,40 +23008,40 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Pansoral Repair Gel Reparador
 15ml</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/pansoral-repair-gel-reparador-5036327.html</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>5036327</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -23491,17 +23491,17 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Refill Interdental Brushes ISO5
@@ -23509,40 +23509,40 @@
 3 un</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/refill-interdental-brushes-iso5-8547079.html</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>8547079</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Refills Interdental Brushes Fine
@@ -23550,40 +23550,40 @@
 4 un</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/refills-interdental-brushes-fine-8414341.html</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>8414341</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Refills Interdental Brushes Fine
@@ -23591,23 +23591,23 @@
 4 un</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/refills-interdental-brushes-fine-8414342.html</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>8414342</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -23696,40 +23696,40 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Spray Cicallium
 15 ml</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/spray-cicallium-6637665.html</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>6637665</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -23858,17 +23858,17 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Trio Compact Interdental Brushes Fine
@@ -23876,40 +23876,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/trio-compact-interdental-brushes-fine-8414367.html</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>8414367</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Trio Compact Interdental Brushes Fine Large
@@ -23917,40 +23917,40 @@
 1 un</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/trio-compact-interdental-brushes-fine-large-8414338.html</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr"/>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>8414338</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>Oral Care</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>Elgydium
 Triocompact Escovilhão Estreito Misto
@@ -23958,23 +23958,23 @@
 1 un</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/triocompact-escovilhao-estreito-misto-8420699.html</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
         <is>
           <t>8420699</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -24295,40 +24295,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Dexeryl</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Creme Emoliente Pele Seca ou Atópica
 Creme Corpo para Pele Seca e Atópica
 250 gr</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-emoliente-pele-seca-ou-atopica-6037808.html</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>6037808</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -24562,38 +24562,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Dermalibour+ Barrier Irritaded Aggressed Skin
 Creme Barreira Protetor Isolante Pele Irritada</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>6554645</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dermalibour-barrier-irritaded-aggressed-skin-452822.html</t>
         </is>
@@ -24790,38 +24790,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Epitheliale Ultra Repair Cream SPF50+
 Creme Protetor Solar Reparador</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>40 ml</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>8478836</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/epitheliale-ultra-repair-cream-spf50-412214.html</t>
         </is>
@@ -25284,38 +25284,38 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Exomega Control Emollient Foaming Gel
 Gel Espuma Calmante Comichão da Pele Atópica</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>6587158</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emollient-foaming-gel-452816.html</t>
         </is>
@@ -25775,38 +25775,38 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Micelar Water Make-Up Removing
 Água Micelar Desmaquilhante Pele Sensível</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>8690955</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/micelar-water-make-up-removing-443917.html</t>
         </is>
@@ -26117,38 +26117,38 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Xeracalm AD Lipid-Replenishing Cleansing Oil
 Óleo de Limpeza Pele Seca Atópica Comichão</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>1000 ml</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>8804160</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/xeracalm-ad-lipid-replenishing-cleansing-oil-457216.html</t>
         </is>
@@ -26727,76 +26727,76 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Sensinol Soothing Cleansing Oil
 Óleo Lavante Calmante Pele Seca Comichão</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>6037950</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sensinol-soothing-cleansing-oil-415426.html</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Sensinol Soothing Cleansing Oil
 Óleo Lavante Calmante Pele Seca Comichão</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>6606367</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sensinol-soothing-cleansing-oil-415426.html</t>
         </is>
@@ -26879,38 +26879,38 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Flax Volume Fine Hair Shampoo
 Champô Fibras de Linho BIO Volume Cabelo Fino</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>5221797</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
         </is>
@@ -27145,38 +27145,38 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Shampoo
 Champô Manga Nutritivo para Cabelo Seco</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>3018059</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
         </is>
@@ -27259,38 +27259,38 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
 Champô Seco Ortiga BIO Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>8123735</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
         </is>
@@ -27411,38 +27411,38 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
 Champô Seco Aveia Spray Suave Cabelo Normal</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>7831152</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
         </is>
@@ -27943,152 +27943,152 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Forticea Strengthening Revitalizing Shampoo
 Champô Fortificante Todos Tipos de Cabelo</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>7630905</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-343991.html</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>6633968</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>7610972</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Naturia Gentle Micellair Shampoo
 Champô Suave Uso Frequente e Familiar</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>5522799</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/naturia-gentle-micellair-shampoo-343992.html</t>
         </is>
